--- a/datos_municipio.xlsx
+++ b/datos_municipio.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="4" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="localidades" sheetId="1" state="visible" r:id="rId1"/>
@@ -18751,7 +18751,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">

--- a/datos_municipio.xlsx
+++ b/datos_municipio.xlsx
@@ -4,7 +4,7 @@
   <workbookPr date1904="0"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="localidades" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,6 +13,9 @@
     <sheet name="teams" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="users" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">calles!$A$1:$D$982</definedName>
+  </definedNames>
   <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -4479,7 +4482,10 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.7109375"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -4495,7 +4501,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4509,7 +4515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4523,7 +4529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4551,7 +4557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="1">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4579,7 +4585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="1">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4593,7 +4599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4607,7 +4613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="1">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4621,7 +4627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="1">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4635,7 +4641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4649,7 +4655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="1">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4663,7 +4669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="1">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4677,7 +4683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4691,7 +4697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="1">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4705,7 +4711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="1">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4719,7 +4725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="1">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4733,7 +4739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4747,7 +4753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="1">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4761,7 +4767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="1">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4775,7 +4781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="1">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4789,7 +4795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="1">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4803,7 +4809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4817,7 +4823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4831,7 +4837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="1">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4845,7 +4851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="1">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4859,7 +4865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="1">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4873,7 +4879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="1">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4887,7 +4893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="1">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4901,7 +4907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4915,7 +4921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="1">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4929,7 +4935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="1">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4943,7 +4949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="1">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4957,7 +4963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="1">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4971,7 +4977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4985,7 +4991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4999,7 +5005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="1">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5013,7 +5019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="1">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5027,7 +5033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5041,7 +5047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="1">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5055,7 +5061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="1">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5083,7 +5089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5097,7 +5103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5111,7 +5117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="1">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5125,7 +5131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="1">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5139,7 +5145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5153,7 +5159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="1">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5167,7 +5173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="1">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5181,7 +5187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="1">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5195,7 +5201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="1">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5209,7 +5215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5223,7 +5229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="1">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5237,7 +5243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5251,7 +5257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5265,7 +5271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="1">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5279,7 +5285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5293,7 +5299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="1">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5307,7 +5313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="1">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5321,7 +5327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="1">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5335,7 +5341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="1">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5349,7 +5355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="1">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5363,7 +5369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="1">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5377,7 +5383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="1">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5391,7 +5397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="1">
       <c r="A66">
         <v>65</v>
       </c>
@@ -5405,7 +5411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="1">
       <c r="A67">
         <v>66</v>
       </c>
@@ -5419,7 +5425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="1">
       <c r="A68">
         <v>67</v>
       </c>
@@ -5433,7 +5439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69">
         <v>68</v>
       </c>
@@ -5447,7 +5453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70">
         <v>69</v>
       </c>
@@ -5461,7 +5467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="1">
       <c r="A71">
         <v>70</v>
       </c>
@@ -5475,7 +5481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72">
         <v>71</v>
       </c>
@@ -5489,7 +5495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="1">
       <c r="A73">
         <v>72</v>
       </c>
@@ -5503,7 +5509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="1">
       <c r="A74">
         <v>73</v>
       </c>
@@ -5517,7 +5523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75">
         <v>74</v>
       </c>
@@ -5531,7 +5537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76">
         <v>75</v>
       </c>
@@ -5545,7 +5551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="1">
       <c r="A77">
         <v>76</v>
       </c>
@@ -5559,7 +5565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="1">
       <c r="A78">
         <v>77</v>
       </c>
@@ -5573,7 +5579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="1">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5587,7 +5593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="1">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5601,7 +5607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="1">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5615,7 +5621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="1">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5629,7 +5635,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="1">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5643,7 +5649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="1">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5657,7 +5663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5671,7 +5677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="1">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5685,7 +5691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="1">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5699,7 +5705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5713,7 +5719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5727,7 +5733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="1">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5741,7 +5747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="1">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5755,7 +5761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5769,7 +5775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="1">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5783,7 +5789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="1">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5797,7 +5803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="1">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5811,7 +5817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5825,7 +5831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="1">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5839,7 +5845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="1">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5853,7 +5859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="1">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5867,7 +5873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5881,7 +5887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="1">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5895,7 +5901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="1">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5909,7 +5915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5923,7 +5929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5937,7 +5943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="1">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5951,7 +5957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="1">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5965,7 +5971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="1">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5979,7 +5985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5993,7 +5999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6007,7 +6013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="1">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6021,7 +6027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="1">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6035,7 +6041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6049,7 +6055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6063,7 +6069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6091,7 +6097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="1">
       <c r="A116">
         <v>115</v>
       </c>
@@ -6105,7 +6111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="1">
       <c r="A117">
         <v>116</v>
       </c>
@@ -6119,7 +6125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="1">
       <c r="A118">
         <v>117</v>
       </c>
@@ -6133,7 +6139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="1">
       <c r="A119">
         <v>118</v>
       </c>
@@ -6147,7 +6153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="1">
       <c r="A120">
         <v>119</v>
       </c>
@@ -6161,7 +6167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="1">
       <c r="A121">
         <v>120</v>
       </c>
@@ -6175,7 +6181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122">
         <v>121</v>
       </c>
@@ -6189,7 +6195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="1">
       <c r="A123">
         <v>122</v>
       </c>
@@ -6203,7 +6209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124">
         <v>123</v>
       </c>
@@ -6217,7 +6223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="1">
       <c r="A125">
         <v>124</v>
       </c>
@@ -6231,7 +6237,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="1">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6245,7 +6251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6259,7 +6265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6273,7 +6279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="1">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6287,7 +6293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="1">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6301,7 +6307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="1">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6315,7 +6321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="1">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6329,7 +6335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="1">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6343,7 +6349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="1">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6357,7 +6363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="1">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6371,7 +6377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6385,7 +6391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="1">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6399,7 +6405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="1">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6413,7 +6419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="1">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6427,7 +6433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="1">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6441,7 +6447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="1">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6455,7 +6461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="1">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6469,7 +6475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6483,7 +6489,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="1">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6497,7 +6503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="1">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6511,7 +6517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="1">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6525,7 +6531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="1">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6539,7 +6545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="1">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6553,7 +6559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="1">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6567,7 +6573,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="1">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6581,7 +6587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="1">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6595,7 +6601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="1">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6609,7 +6615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="1">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6623,7 +6629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="1">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6637,7 +6643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="1">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6651,7 +6657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="1">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6665,7 +6671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="1">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6679,7 +6685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="1">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="1">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6707,7 +6713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="1">
       <c r="A160">
         <v>159</v>
       </c>
@@ -6721,7 +6727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="1">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6735,7 +6741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="1">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6749,7 +6755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="1">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6763,7 +6769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="1">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6777,7 +6783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="1">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6791,7 +6797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="1">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6805,7 +6811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="1">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6819,7 +6825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="1">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6833,7 +6839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="1">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6847,7 +6853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="1">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6861,7 +6867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="1">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6875,7 +6881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="1">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6889,7 +6895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="1">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6903,7 +6909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="1">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6917,7 +6923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="1">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6931,7 +6937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="1">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6945,7 +6951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="1">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6959,7 +6965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="1">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6973,7 +6979,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="1">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6987,7 +6993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="1">
       <c r="A180">
         <v>179</v>
       </c>
@@ -7001,7 +7007,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="1">
       <c r="A181">
         <v>180</v>
       </c>
@@ -7015,7 +7021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="1">
       <c r="A182">
         <v>181</v>
       </c>
@@ -7029,7 +7035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="1">
       <c r="A183">
         <v>182</v>
       </c>
@@ -7043,7 +7049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" hidden="1">
       <c r="A184">
         <v>183</v>
       </c>
@@ -7057,7 +7063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="1">
       <c r="A185">
         <v>184</v>
       </c>
@@ -7071,7 +7077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="1">
       <c r="A186">
         <v>185</v>
       </c>
@@ -7085,7 +7091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" hidden="1">
       <c r="A187">
         <v>186</v>
       </c>
@@ -7099,7 +7105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="1">
       <c r="A188">
         <v>187</v>
       </c>
@@ -7113,7 +7119,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" hidden="1">
       <c r="A189">
         <v>188</v>
       </c>
@@ -7127,7 +7133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="1">
       <c r="A190">
         <v>189</v>
       </c>
@@ -7141,7 +7147,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="1">
       <c r="A191">
         <v>190</v>
       </c>
@@ -7155,7 +7161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" hidden="1">
       <c r="A192">
         <v>191</v>
       </c>
@@ -7169,7 +7175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" hidden="1">
       <c r="A193">
         <v>192</v>
       </c>
@@ -7183,7 +7189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" hidden="1">
       <c r="A194">
         <v>193</v>
       </c>
@@ -7197,7 +7203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" hidden="1">
       <c r="A195">
         <v>194</v>
       </c>
@@ -7211,7 +7217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="1">
       <c r="A196">
         <v>195</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197">
         <v>196</v>
       </c>
@@ -7239,7 +7245,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" hidden="1">
       <c r="A198">
         <v>197</v>
       </c>
@@ -7253,7 +7259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" hidden="1">
       <c r="A199">
         <v>198</v>
       </c>
@@ -7267,7 +7273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" hidden="1">
       <c r="A200">
         <v>199</v>
       </c>
@@ -7281,7 +7287,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" hidden="1">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7295,7 +7301,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="1">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7309,7 +7315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="1">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7323,7 +7329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="1">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7337,7 +7343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="1">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" hidden="1">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7365,7 +7371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" hidden="1">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7379,7 +7385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" hidden="1">
       <c r="A208">
         <v>207</v>
       </c>
@@ -7393,7 +7399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="1">
       <c r="A209">
         <v>208</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" hidden="1">
       <c r="A210">
         <v>209</v>
       </c>
@@ -7421,7 +7427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="1">
       <c r="A211">
         <v>210</v>
       </c>
@@ -7435,7 +7441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" hidden="1">
       <c r="A212">
         <v>211</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" hidden="1">
       <c r="A213">
         <v>212</v>
       </c>
@@ -7463,7 +7469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" hidden="1">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7477,7 +7483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" hidden="1">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7491,7 +7497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" hidden="1">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7505,7 +7511,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="1">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7519,7 +7525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" hidden="1">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="1">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7547,7 +7553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" hidden="1">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7561,7 +7567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" hidden="1">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7575,7 +7581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" hidden="1">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7589,7 +7595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="1">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7603,7 +7609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="1">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7617,7 +7623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="1">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7631,7 +7637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" hidden="1">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7645,7 +7651,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" hidden="1">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7659,7 +7665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" hidden="1">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7673,7 +7679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" hidden="1">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" hidden="1">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7701,7 +7707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" hidden="1">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7715,7 +7721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" hidden="1">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7729,7 +7735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" hidden="1">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7743,7 +7749,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" hidden="1">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7757,7 +7763,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" hidden="1">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7771,7 +7777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" hidden="1">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7785,7 +7791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" hidden="1">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7799,7 +7805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" hidden="1">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" hidden="1">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7827,7 +7833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" hidden="1">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7841,7 +7847,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" hidden="1">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7855,7 +7861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" hidden="1">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7869,7 +7875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" hidden="1">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7883,7 +7889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" hidden="1">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7897,7 +7903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" hidden="1">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7911,7 +7917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" hidden="1">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7925,7 +7931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" hidden="1">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7939,7 +7945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" hidden="1">
       <c r="A248">
         <v>247</v>
       </c>
@@ -7953,7 +7959,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" hidden="1">
       <c r="A249">
         <v>248</v>
       </c>
@@ -7967,7 +7973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" hidden="1">
       <c r="A250">
         <v>249</v>
       </c>
@@ -7981,7 +7987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" hidden="1">
       <c r="A251">
         <v>250</v>
       </c>
@@ -7995,7 +8001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" hidden="1">
       <c r="A252">
         <v>251</v>
       </c>
@@ -8009,7 +8015,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" hidden="1">
       <c r="A253">
         <v>252</v>
       </c>
@@ -8023,7 +8029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" hidden="1">
       <c r="A254">
         <v>253</v>
       </c>
@@ -8037,7 +8043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" hidden="1">
       <c r="A255">
         <v>254</v>
       </c>
@@ -8051,7 +8057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" hidden="1">
       <c r="A256">
         <v>255</v>
       </c>
@@ -8065,7 +8071,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" hidden="1">
       <c r="A257">
         <v>256</v>
       </c>
@@ -8079,7 +8085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" hidden="1">
       <c r="A258">
         <v>257</v>
       </c>
@@ -8093,7 +8099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" hidden="1">
       <c r="A259">
         <v>258</v>
       </c>
@@ -8107,7 +8113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" hidden="1">
       <c r="A260">
         <v>259</v>
       </c>
@@ -8121,7 +8127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" hidden="1">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8135,7 +8141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" hidden="1">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8149,7 +8155,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" hidden="1">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8163,7 +8169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" hidden="1">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8177,7 +8183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" hidden="1">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8191,7 +8197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" hidden="1">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8205,7 +8211,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" hidden="1">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8219,7 +8225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" hidden="1">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8233,7 +8239,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" hidden="1">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8247,7 +8253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" hidden="1">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8261,7 +8267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" hidden="1">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8275,7 +8281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" hidden="1">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8289,7 +8295,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" hidden="1">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8303,7 +8309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" hidden="1">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8317,7 +8323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" hidden="1">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8331,7 +8337,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" hidden="1">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8345,7 +8351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" hidden="1">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8359,7 +8365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" hidden="1">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8373,7 +8379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" hidden="1">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8387,7 +8393,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" hidden="1">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8401,7 +8407,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" hidden="1">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8415,7 +8421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" hidden="1">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8429,7 +8435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" hidden="1">
       <c r="A283">
         <v>282</v>
       </c>
@@ -8443,7 +8449,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" hidden="1">
       <c r="A284">
         <v>283</v>
       </c>
@@ -8457,7 +8463,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" hidden="1">
       <c r="A285">
         <v>284</v>
       </c>
@@ -8471,7 +8477,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" hidden="1">
       <c r="A286">
         <v>285</v>
       </c>
@@ -8485,7 +8491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" hidden="1">
       <c r="A287">
         <v>286</v>
       </c>
@@ -8499,7 +8505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" hidden="1">
       <c r="A288">
         <v>287</v>
       </c>
@@ -8513,7 +8519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" hidden="1">
       <c r="A289">
         <v>288</v>
       </c>
@@ -8527,7 +8533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" hidden="1">
       <c r="A290">
         <v>289</v>
       </c>
@@ -8541,7 +8547,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" hidden="1">
       <c r="A291">
         <v>290</v>
       </c>
@@ -8555,7 +8561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" hidden="1">
       <c r="A292">
         <v>291</v>
       </c>
@@ -8569,7 +8575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" hidden="1">
       <c r="A293">
         <v>292</v>
       </c>
@@ -8583,7 +8589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" hidden="1">
       <c r="A294">
         <v>293</v>
       </c>
@@ -8597,7 +8603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" hidden="1">
       <c r="A295">
         <v>294</v>
       </c>
@@ -8611,7 +8617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" hidden="1">
       <c r="A296">
         <v>295</v>
       </c>
@@ -8625,7 +8631,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" hidden="1">
       <c r="A297">
         <v>296</v>
       </c>
@@ -8639,7 +8645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" hidden="1">
       <c r="A298">
         <v>297</v>
       </c>
@@ -8653,7 +8659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" hidden="1">
       <c r="A299">
         <v>298</v>
       </c>
@@ -8667,7 +8673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" hidden="1">
       <c r="A300">
         <v>299</v>
       </c>
@@ -8681,7 +8687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" hidden="1">
       <c r="A301">
         <v>300</v>
       </c>
@@ -8695,7 +8701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" hidden="1">
       <c r="A302">
         <v>301</v>
       </c>
@@ -8709,7 +8715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" hidden="1">
       <c r="A303">
         <v>302</v>
       </c>
@@ -8723,7 +8729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" hidden="1">
       <c r="A304">
         <v>303</v>
       </c>
@@ -8737,7 +8743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" hidden="1">
       <c r="A305">
         <v>304</v>
       </c>
@@ -8751,7 +8757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" hidden="1">
       <c r="A306">
         <v>305</v>
       </c>
@@ -8765,7 +8771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" hidden="1">
       <c r="A307">
         <v>306</v>
       </c>
@@ -8779,7 +8785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" hidden="1">
       <c r="A308">
         <v>307</v>
       </c>
@@ -8793,7 +8799,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" hidden="1">
       <c r="A309">
         <v>308</v>
       </c>
@@ -8807,7 +8813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" hidden="1">
       <c r="A310">
         <v>309</v>
       </c>
@@ -8821,7 +8827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" hidden="1">
       <c r="A311">
         <v>310</v>
       </c>
@@ -8835,7 +8841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312">
         <v>311</v>
       </c>
@@ -8849,7 +8855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" hidden="1">
       <c r="A313">
         <v>312</v>
       </c>
@@ -8863,7 +8869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" hidden="1">
       <c r="A314">
         <v>313</v>
       </c>
@@ -8877,7 +8883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" hidden="1">
       <c r="A315">
         <v>314</v>
       </c>
@@ -8891,7 +8897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" hidden="1">
       <c r="A316">
         <v>315</v>
       </c>
@@ -8905,7 +8911,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317">
         <v>316</v>
       </c>
@@ -8919,7 +8925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" hidden="1">
       <c r="A318">
         <v>317</v>
       </c>
@@ -8933,7 +8939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" hidden="1">
       <c r="A319">
         <v>318</v>
       </c>
@@ -8947,7 +8953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" hidden="1">
       <c r="A320">
         <v>319</v>
       </c>
@@ -8961,7 +8967,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" hidden="1">
       <c r="A321">
         <v>320</v>
       </c>
@@ -8975,7 +8981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" hidden="1">
       <c r="A322">
         <v>321</v>
       </c>
@@ -8989,7 +8995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" hidden="1">
       <c r="A323">
         <v>322</v>
       </c>
@@ -9003,7 +9009,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" hidden="1">
       <c r="A324">
         <v>323</v>
       </c>
@@ -9017,7 +9023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" hidden="1">
       <c r="A325">
         <v>324</v>
       </c>
@@ -9031,7 +9037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" hidden="1">
       <c r="A326">
         <v>325</v>
       </c>
@@ -9045,7 +9051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" hidden="1">
       <c r="A327">
         <v>326</v>
       </c>
@@ -9059,7 +9065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" hidden="1">
       <c r="A328">
         <v>327</v>
       </c>
@@ -9073,7 +9079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" hidden="1">
       <c r="A329">
         <v>328</v>
       </c>
@@ -9087,7 +9093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" hidden="1">
       <c r="A330">
         <v>329</v>
       </c>
@@ -9101,7 +9107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" hidden="1">
       <c r="A331">
         <v>330</v>
       </c>
@@ -9115,7 +9121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" hidden="1">
       <c r="A332">
         <v>331</v>
       </c>
@@ -9129,7 +9135,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" hidden="1">
       <c r="A333">
         <v>332</v>
       </c>
@@ -9143,7 +9149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" hidden="1">
       <c r="A334">
         <v>333</v>
       </c>
@@ -9157,7 +9163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" hidden="1">
       <c r="A335">
         <v>334</v>
       </c>
@@ -9171,7 +9177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" hidden="1">
       <c r="A336">
         <v>335</v>
       </c>
@@ -9185,7 +9191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" hidden="1">
       <c r="A337">
         <v>336</v>
       </c>
@@ -9199,7 +9205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" hidden="1">
       <c r="A338">
         <v>337</v>
       </c>
@@ -9213,7 +9219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" hidden="1">
       <c r="A339">
         <v>338</v>
       </c>
@@ -9227,7 +9233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" hidden="1">
       <c r="A340">
         <v>339</v>
       </c>
@@ -9241,7 +9247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" hidden="1">
       <c r="A341">
         <v>340</v>
       </c>
@@ -9255,7 +9261,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" hidden="1">
       <c r="A342">
         <v>341</v>
       </c>
@@ -9269,7 +9275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" hidden="1">
       <c r="A343">
         <v>342</v>
       </c>
@@ -9283,7 +9289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" hidden="1">
       <c r="A344">
         <v>343</v>
       </c>
@@ -9297,7 +9303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" hidden="1">
       <c r="A345">
         <v>344</v>
       </c>
@@ -9311,7 +9317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" hidden="1">
       <c r="A346">
         <v>345</v>
       </c>
@@ -9325,7 +9331,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" hidden="1">
       <c r="A347">
         <v>346</v>
       </c>
@@ -9339,7 +9345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" hidden="1">
       <c r="A348">
         <v>347</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" hidden="1">
       <c r="A349">
         <v>348</v>
       </c>
@@ -9367,7 +9373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" hidden="1">
       <c r="A350">
         <v>349</v>
       </c>
@@ -9381,7 +9387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" hidden="1">
       <c r="A351">
         <v>350</v>
       </c>
@@ -9395,7 +9401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" hidden="1">
       <c r="A352">
         <v>351</v>
       </c>
@@ -9409,7 +9415,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" hidden="1">
       <c r="A353">
         <v>352</v>
       </c>
@@ -9423,7 +9429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" hidden="1">
       <c r="A354">
         <v>353</v>
       </c>
@@ -9437,7 +9443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" hidden="1">
       <c r="A355">
         <v>354</v>
       </c>
@@ -9451,7 +9457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" hidden="1">
       <c r="A356">
         <v>355</v>
       </c>
@@ -9465,7 +9471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" hidden="1">
       <c r="A357">
         <v>356</v>
       </c>
@@ -9479,7 +9485,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" hidden="1">
       <c r="A358">
         <v>357</v>
       </c>
@@ -9493,7 +9499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" hidden="1">
       <c r="A359">
         <v>358</v>
       </c>
@@ -9507,7 +9513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" hidden="1">
       <c r="A360">
         <v>359</v>
       </c>
@@ -9521,7 +9527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" hidden="1">
       <c r="A361">
         <v>360</v>
       </c>
@@ -9535,7 +9541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" hidden="1">
       <c r="A362">
         <v>361</v>
       </c>
@@ -9549,7 +9555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" hidden="1">
       <c r="A363">
         <v>362</v>
       </c>
@@ -9563,7 +9569,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" hidden="1">
       <c r="A364">
         <v>363</v>
       </c>
@@ -9577,7 +9583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" hidden="1">
       <c r="A365">
         <v>364</v>
       </c>
@@ -9591,7 +9597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" hidden="1">
       <c r="A366">
         <v>365</v>
       </c>
@@ -9605,7 +9611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" hidden="1">
       <c r="A367">
         <v>366</v>
       </c>
@@ -9619,7 +9625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" hidden="1">
       <c r="A368">
         <v>367</v>
       </c>
@@ -9633,7 +9639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" hidden="1">
       <c r="A369">
         <v>368</v>
       </c>
@@ -9647,7 +9653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" hidden="1">
       <c r="A370">
         <v>369</v>
       </c>
@@ -9661,7 +9667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" hidden="1">
       <c r="A371">
         <v>370</v>
       </c>
@@ -9675,7 +9681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" hidden="1">
       <c r="A372">
         <v>371</v>
       </c>
@@ -9689,7 +9695,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" hidden="1">
       <c r="A373">
         <v>372</v>
       </c>
@@ -9703,7 +9709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" hidden="1">
       <c r="A374">
         <v>373</v>
       </c>
@@ -9717,7 +9723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" hidden="1">
       <c r="A375">
         <v>374</v>
       </c>
@@ -9731,7 +9737,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" hidden="1">
       <c r="A376">
         <v>375</v>
       </c>
@@ -9745,7 +9751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" hidden="1">
       <c r="A377">
         <v>376</v>
       </c>
@@ -9759,7 +9765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" hidden="1">
       <c r="A378">
         <v>377</v>
       </c>
@@ -9773,7 +9779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" hidden="1">
       <c r="A379">
         <v>378</v>
       </c>
@@ -9787,7 +9793,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" hidden="1">
       <c r="A380">
         <v>379</v>
       </c>
@@ -9801,7 +9807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" hidden="1">
       <c r="A381">
         <v>380</v>
       </c>
@@ -9815,7 +9821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" hidden="1">
       <c r="A382">
         <v>381</v>
       </c>
@@ -9829,7 +9835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" hidden="1">
       <c r="A383">
         <v>382</v>
       </c>
@@ -9843,7 +9849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" hidden="1">
       <c r="A384">
         <v>383</v>
       </c>
@@ -9857,7 +9863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" hidden="1">
       <c r="A385">
         <v>384</v>
       </c>
@@ -9871,7 +9877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" hidden="1">
       <c r="A386">
         <v>385</v>
       </c>
@@ -9885,7 +9891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" hidden="1">
       <c r="A387">
         <v>386</v>
       </c>
@@ -9899,7 +9905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" hidden="1">
       <c r="A388">
         <v>387</v>
       </c>
@@ -9913,7 +9919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" hidden="1">
       <c r="A389">
         <v>388</v>
       </c>
@@ -9927,7 +9933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" hidden="1">
       <c r="A390">
         <v>389</v>
       </c>
@@ -9941,7 +9947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" hidden="1">
       <c r="A391">
         <v>390</v>
       </c>
@@ -9955,7 +9961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" hidden="1">
       <c r="A392">
         <v>391</v>
       </c>
@@ -9969,7 +9975,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" hidden="1">
       <c r="A393">
         <v>392</v>
       </c>
@@ -9983,7 +9989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" hidden="1">
       <c r="A394">
         <v>393</v>
       </c>
@@ -9997,7 +10003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" hidden="1">
       <c r="A395">
         <v>394</v>
       </c>
@@ -10011,7 +10017,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" hidden="1">
       <c r="A396">
         <v>395</v>
       </c>
@@ -10025,7 +10031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" hidden="1">
       <c r="A397">
         <v>396</v>
       </c>
@@ -10039,7 +10045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" hidden="1">
       <c r="A398">
         <v>397</v>
       </c>
@@ -10053,7 +10059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" hidden="1">
       <c r="A399">
         <v>398</v>
       </c>
@@ -10067,7 +10073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" hidden="1">
       <c r="A400">
         <v>399</v>
       </c>
@@ -10081,7 +10087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" hidden="1">
       <c r="A401">
         <v>400</v>
       </c>
@@ -10095,7 +10101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" hidden="1">
       <c r="A402">
         <v>401</v>
       </c>
@@ -10109,7 +10115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" hidden="1">
       <c r="A403">
         <v>402</v>
       </c>
@@ -10123,7 +10129,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" hidden="1">
       <c r="A404">
         <v>403</v>
       </c>
@@ -10137,7 +10143,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" hidden="1">
       <c r="A405">
         <v>404</v>
       </c>
@@ -10151,7 +10157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" hidden="1">
       <c r="A406">
         <v>405</v>
       </c>
@@ -10165,7 +10171,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" hidden="1">
       <c r="A407">
         <v>406</v>
       </c>
@@ -10179,7 +10185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" hidden="1">
       <c r="A408">
         <v>407</v>
       </c>
@@ -10193,7 +10199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" hidden="1">
       <c r="A409">
         <v>408</v>
       </c>
@@ -10207,7 +10213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" hidden="1">
       <c r="A410">
         <v>409</v>
       </c>
@@ -10221,7 +10227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" hidden="1">
       <c r="A411">
         <v>410</v>
       </c>
@@ -10235,7 +10241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" hidden="1">
       <c r="A412">
         <v>411</v>
       </c>
@@ -10249,7 +10255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413">
         <v>412</v>
       </c>
@@ -10263,7 +10269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" hidden="1">
       <c r="A414">
         <v>413</v>
       </c>
@@ -10277,7 +10283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" hidden="1">
       <c r="A415">
         <v>414</v>
       </c>
@@ -10291,7 +10297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" hidden="1">
       <c r="A416">
         <v>415</v>
       </c>
@@ -10305,7 +10311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" hidden="1">
       <c r="A417">
         <v>416</v>
       </c>
@@ -10319,7 +10325,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" hidden="1">
       <c r="A418">
         <v>417</v>
       </c>
@@ -10333,7 +10339,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" hidden="1">
       <c r="A419">
         <v>418</v>
       </c>
@@ -10347,7 +10353,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" hidden="1">
       <c r="A420">
         <v>419</v>
       </c>
@@ -10361,7 +10367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" hidden="1">
       <c r="A421">
         <v>420</v>
       </c>
@@ -10375,7 +10381,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422">
         <v>421</v>
       </c>
@@ -10389,7 +10395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" hidden="1">
       <c r="A423">
         <v>422</v>
       </c>
@@ -10403,7 +10409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" hidden="1">
       <c r="A424">
         <v>423</v>
       </c>
@@ -10417,7 +10423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" hidden="1">
       <c r="A425">
         <v>424</v>
       </c>
@@ -10431,7 +10437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" hidden="1">
       <c r="A426">
         <v>425</v>
       </c>
@@ -10445,7 +10451,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" hidden="1">
       <c r="A427">
         <v>426</v>
       </c>
@@ -10459,7 +10465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" hidden="1">
       <c r="A428">
         <v>427</v>
       </c>
@@ -10473,7 +10479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" hidden="1">
       <c r="A429">
         <v>428</v>
       </c>
@@ -10487,7 +10493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" hidden="1">
       <c r="A430">
         <v>429</v>
       </c>
@@ -10501,7 +10507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" hidden="1">
       <c r="A431">
         <v>430</v>
       </c>
@@ -10515,7 +10521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" hidden="1">
       <c r="A432">
         <v>431</v>
       </c>
@@ -10529,7 +10535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" hidden="1">
       <c r="A433">
         <v>432</v>
       </c>
@@ -10543,7 +10549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434">
         <v>433</v>
       </c>
@@ -10557,7 +10563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" hidden="1">
       <c r="A435">
         <v>434</v>
       </c>
@@ -10571,7 +10577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" hidden="1">
       <c r="A436">
         <v>435</v>
       </c>
@@ -10585,7 +10591,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" hidden="1">
       <c r="A437">
         <v>436</v>
       </c>
@@ -10599,7 +10605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" hidden="1">
       <c r="A438">
         <v>437</v>
       </c>
@@ -10613,7 +10619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" hidden="1">
       <c r="A439">
         <v>438</v>
       </c>
@@ -10627,7 +10633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" hidden="1">
       <c r="A440">
         <v>439</v>
       </c>
@@ -10641,7 +10647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" hidden="1">
       <c r="A441">
         <v>440</v>
       </c>
@@ -10655,7 +10661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" hidden="1">
       <c r="A442">
         <v>441</v>
       </c>
@@ -10669,7 +10675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" hidden="1">
       <c r="A443">
         <v>442</v>
       </c>
@@ -10683,7 +10689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" hidden="1">
       <c r="A444">
         <v>443</v>
       </c>
@@ -10697,7 +10703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" hidden="1">
       <c r="A445">
         <v>444</v>
       </c>
@@ -10711,7 +10717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" hidden="1">
       <c r="A446">
         <v>445</v>
       </c>
@@ -10725,7 +10731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" hidden="1">
       <c r="A447">
         <v>446</v>
       </c>
@@ -10739,7 +10745,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" hidden="1">
       <c r="A448">
         <v>447</v>
       </c>
@@ -10753,7 +10759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" hidden="1">
       <c r="A449">
         <v>448</v>
       </c>
@@ -10767,7 +10773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" hidden="1">
       <c r="A450">
         <v>449</v>
       </c>
@@ -10781,7 +10787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" hidden="1">
       <c r="A451">
         <v>450</v>
       </c>
@@ -10795,7 +10801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" hidden="1">
       <c r="A452">
         <v>451</v>
       </c>
@@ -10809,7 +10815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" hidden="1">
       <c r="A453">
         <v>452</v>
       </c>
@@ -10823,7 +10829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" hidden="1">
       <c r="A454">
         <v>453</v>
       </c>
@@ -10837,7 +10843,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" hidden="1">
       <c r="A455">
         <v>454</v>
       </c>
@@ -10851,7 +10857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" hidden="1">
       <c r="A456">
         <v>455</v>
       </c>
@@ -10865,7 +10871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" hidden="1">
       <c r="A457">
         <v>456</v>
       </c>
@@ -10879,7 +10885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" hidden="1">
       <c r="A458">
         <v>457</v>
       </c>
@@ -10893,7 +10899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" hidden="1">
       <c r="A459">
         <v>458</v>
       </c>
@@ -10907,7 +10913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" hidden="1">
       <c r="A460">
         <v>459</v>
       </c>
@@ -10921,7 +10927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" hidden="1">
       <c r="A461">
         <v>460</v>
       </c>
@@ -10935,7 +10941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" hidden="1">
       <c r="A462">
         <v>461</v>
       </c>
@@ -10949,7 +10955,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" hidden="1">
       <c r="A463">
         <v>462</v>
       </c>
@@ -10963,7 +10969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" hidden="1">
       <c r="A464">
         <v>463</v>
       </c>
@@ -10977,7 +10983,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" hidden="1">
       <c r="A465">
         <v>464</v>
       </c>
@@ -10991,7 +10997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" hidden="1">
       <c r="A466">
         <v>465</v>
       </c>
@@ -11005,7 +11011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" hidden="1">
       <c r="A467">
         <v>466</v>
       </c>
@@ -11019,7 +11025,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" hidden="1">
       <c r="A468">
         <v>467</v>
       </c>
@@ -11033,7 +11039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" hidden="1">
       <c r="A469">
         <v>468</v>
       </c>
@@ -11047,7 +11053,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" hidden="1">
       <c r="A470">
         <v>469</v>
       </c>
@@ -11061,7 +11067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" hidden="1">
       <c r="A471">
         <v>470</v>
       </c>
@@ -11075,7 +11081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" hidden="1">
       <c r="A472">
         <v>471</v>
       </c>
@@ -11089,7 +11095,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" hidden="1">
       <c r="A473">
         <v>472</v>
       </c>
@@ -11103,7 +11109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" hidden="1">
       <c r="A474">
         <v>473</v>
       </c>
@@ -11117,7 +11123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" hidden="1">
       <c r="A475">
         <v>474</v>
       </c>
@@ -11131,7 +11137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" hidden="1">
       <c r="A476">
         <v>475</v>
       </c>
@@ -11145,7 +11151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" hidden="1">
       <c r="A477">
         <v>476</v>
       </c>
@@ -11159,7 +11165,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" hidden="1">
       <c r="A478">
         <v>477</v>
       </c>
@@ -11173,7 +11179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" hidden="1">
       <c r="A479">
         <v>478</v>
       </c>
@@ -11187,7 +11193,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" hidden="1">
       <c r="A480">
         <v>479</v>
       </c>
@@ -11201,7 +11207,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" hidden="1">
       <c r="A481">
         <v>480</v>
       </c>
@@ -11215,7 +11221,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" hidden="1">
       <c r="A482">
         <v>481</v>
       </c>
@@ -11229,7 +11235,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" hidden="1">
       <c r="A483">
         <v>482</v>
       </c>
@@ -11243,7 +11249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" hidden="1">
       <c r="A484">
         <v>483</v>
       </c>
@@ -11257,7 +11263,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" hidden="1">
       <c r="A485">
         <v>484</v>
       </c>
@@ -11271,7 +11277,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" hidden="1">
       <c r="A486">
         <v>485</v>
       </c>
@@ -11285,7 +11291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" hidden="1">
       <c r="A487">
         <v>486</v>
       </c>
@@ -11299,7 +11305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" hidden="1">
       <c r="A488">
         <v>487</v>
       </c>
@@ -11313,7 +11319,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" hidden="1">
       <c r="A489">
         <v>488</v>
       </c>
@@ -11327,7 +11333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" hidden="1">
       <c r="A490">
         <v>489</v>
       </c>
@@ -11341,7 +11347,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" hidden="1">
       <c r="A491">
         <v>490</v>
       </c>
@@ -11355,7 +11361,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" hidden="1">
       <c r="A492">
         <v>491</v>
       </c>
@@ -11369,7 +11375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" hidden="1">
       <c r="A493">
         <v>492</v>
       </c>
@@ -11383,7 +11389,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" hidden="1">
       <c r="A494">
         <v>493</v>
       </c>
@@ -11397,7 +11403,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" hidden="1">
       <c r="A495">
         <v>494</v>
       </c>
@@ -11411,7 +11417,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" hidden="1">
       <c r="A496">
         <v>495</v>
       </c>
@@ -11425,7 +11431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" hidden="1">
       <c r="A497">
         <v>496</v>
       </c>
@@ -11439,7 +11445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" hidden="1">
       <c r="A498">
         <v>497</v>
       </c>
@@ -11453,7 +11459,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" hidden="1">
       <c r="A499">
         <v>498</v>
       </c>
@@ -11467,7 +11473,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" hidden="1">
       <c r="A500">
         <v>499</v>
       </c>
@@ -11481,7 +11487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" hidden="1">
       <c r="A501">
         <v>500</v>
       </c>
@@ -11495,7 +11501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" hidden="1">
       <c r="A502">
         <v>501</v>
       </c>
@@ -11509,7 +11515,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" hidden="1">
       <c r="A503">
         <v>502</v>
       </c>
@@ -11523,7 +11529,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" hidden="1">
       <c r="A504">
         <v>503</v>
       </c>
@@ -11537,7 +11543,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" hidden="1">
       <c r="A505">
         <v>504</v>
       </c>
@@ -11551,7 +11557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" hidden="1">
       <c r="A506">
         <v>505</v>
       </c>
@@ -11565,7 +11571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" hidden="1">
       <c r="A507">
         <v>506</v>
       </c>
@@ -11579,7 +11585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" hidden="1">
       <c r="A508">
         <v>507</v>
       </c>
@@ -11593,7 +11599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" hidden="1">
       <c r="A509">
         <v>508</v>
       </c>
@@ -11607,7 +11613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" hidden="1">
       <c r="A510">
         <v>509</v>
       </c>
@@ -11621,7 +11627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" hidden="1">
       <c r="A511">
         <v>510</v>
       </c>
@@ -11635,7 +11641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" hidden="1">
       <c r="A512">
         <v>511</v>
       </c>
@@ -11649,7 +11655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" hidden="1">
       <c r="A513">
         <v>512</v>
       </c>
@@ -11663,7 +11669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" hidden="1">
       <c r="A514">
         <v>513</v>
       </c>
@@ -11677,7 +11683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" hidden="1">
       <c r="A515">
         <v>514</v>
       </c>
@@ -11691,7 +11697,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" hidden="1">
       <c r="A516">
         <v>515</v>
       </c>
@@ -11705,7 +11711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" hidden="1">
       <c r="A517">
         <v>516</v>
       </c>
@@ -11719,7 +11725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" hidden="1">
       <c r="A518">
         <v>517</v>
       </c>
@@ -11733,7 +11739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" hidden="1">
       <c r="A519">
         <v>518</v>
       </c>
@@ -11747,7 +11753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" hidden="1">
       <c r="A520">
         <v>519</v>
       </c>
@@ -11761,7 +11767,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" hidden="1">
       <c r="A521">
         <v>520</v>
       </c>
@@ -11775,7 +11781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" hidden="1">
       <c r="A522">
         <v>521</v>
       </c>
@@ -11789,7 +11795,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" hidden="1">
       <c r="A523">
         <v>522</v>
       </c>
@@ -11803,7 +11809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" hidden="1">
       <c r="A524">
         <v>523</v>
       </c>
@@ -11817,7 +11823,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" hidden="1">
       <c r="A525">
         <v>524</v>
       </c>
@@ -11831,7 +11837,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" hidden="1">
       <c r="A526">
         <v>525</v>
       </c>
@@ -11845,7 +11851,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" hidden="1">
       <c r="A527">
         <v>526</v>
       </c>
@@ -11859,7 +11865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" hidden="1">
       <c r="A528">
         <v>527</v>
       </c>
@@ -11873,7 +11879,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" hidden="1">
       <c r="A529">
         <v>528</v>
       </c>
@@ -11887,7 +11893,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" hidden="1">
       <c r="A530">
         <v>529</v>
       </c>
@@ -11901,7 +11907,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" hidden="1">
       <c r="A531">
         <v>530</v>
       </c>
@@ -11915,7 +11921,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" hidden="1">
       <c r="A532">
         <v>531</v>
       </c>
@@ -11929,7 +11935,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" hidden="1">
       <c r="A533">
         <v>532</v>
       </c>
@@ -11943,7 +11949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" hidden="1">
       <c r="A534">
         <v>533</v>
       </c>
@@ -11957,7 +11963,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" hidden="1">
       <c r="A535">
         <v>534</v>
       </c>
@@ -11971,7 +11977,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" hidden="1">
       <c r="A536">
         <v>535</v>
       </c>
@@ -11985,7 +11991,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" hidden="1">
       <c r="A537">
         <v>536</v>
       </c>
@@ -11999,7 +12005,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" hidden="1">
       <c r="A538">
         <v>537</v>
       </c>
@@ -12013,7 +12019,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" hidden="1">
       <c r="A539">
         <v>538</v>
       </c>
@@ -12027,7 +12033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" hidden="1">
       <c r="A540">
         <v>539</v>
       </c>
@@ -12041,7 +12047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" hidden="1">
       <c r="A541">
         <v>540</v>
       </c>
@@ -12055,7 +12061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" hidden="1">
       <c r="A542">
         <v>541</v>
       </c>
@@ -12069,7 +12075,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" hidden="1">
       <c r="A543">
         <v>542</v>
       </c>
@@ -12083,7 +12089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" hidden="1">
       <c r="A544">
         <v>543</v>
       </c>
@@ -12097,7 +12103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" hidden="1">
       <c r="A545">
         <v>544</v>
       </c>
@@ -12111,7 +12117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" hidden="1">
       <c r="A546">
         <v>545</v>
       </c>
@@ -12125,7 +12131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" hidden="1">
       <c r="A547">
         <v>546</v>
       </c>
@@ -12139,7 +12145,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" hidden="1">
       <c r="A548">
         <v>547</v>
       </c>
@@ -12153,7 +12159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" hidden="1">
       <c r="A549">
         <v>548</v>
       </c>
@@ -12167,7 +12173,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" hidden="1">
       <c r="A550">
         <v>549</v>
       </c>
@@ -12181,7 +12187,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" hidden="1">
       <c r="A551">
         <v>550</v>
       </c>
@@ -12195,7 +12201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="552">
+    <row r="552" hidden="1">
       <c r="A552">
         <v>551</v>
       </c>
@@ -12209,7 +12215,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" hidden="1">
       <c r="A553">
         <v>552</v>
       </c>
@@ -12223,7 +12229,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" hidden="1">
       <c r="A554">
         <v>553</v>
       </c>
@@ -12237,7 +12243,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" hidden="1">
       <c r="A555">
         <v>554</v>
       </c>
@@ -12251,7 +12257,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" hidden="1">
       <c r="A556">
         <v>555</v>
       </c>
@@ -12265,7 +12271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" hidden="1">
       <c r="A557">
         <v>556</v>
       </c>
@@ -12279,7 +12285,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" hidden="1">
       <c r="A558">
         <v>557</v>
       </c>
@@ -12293,7 +12299,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" hidden="1">
       <c r="A559">
         <v>558</v>
       </c>
@@ -12307,7 +12313,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" hidden="1">
       <c r="A560">
         <v>559</v>
       </c>
@@ -12321,7 +12327,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" hidden="1">
       <c r="A561">
         <v>560</v>
       </c>
@@ -12335,7 +12341,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" hidden="1">
       <c r="A562">
         <v>561</v>
       </c>
@@ -12349,7 +12355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" hidden="1">
       <c r="A563">
         <v>562</v>
       </c>
@@ -12363,7 +12369,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" hidden="1">
       <c r="A564">
         <v>563</v>
       </c>
@@ -12377,7 +12383,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" hidden="1">
       <c r="A565">
         <v>564</v>
       </c>
@@ -12391,7 +12397,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" hidden="1">
       <c r="A566">
         <v>565</v>
       </c>
@@ -12405,7 +12411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" hidden="1">
       <c r="A567">
         <v>566</v>
       </c>
@@ -12419,7 +12425,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" hidden="1">
       <c r="A568">
         <v>567</v>
       </c>
@@ -12433,7 +12439,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" hidden="1">
       <c r="A569">
         <v>568</v>
       </c>
@@ -12447,7 +12453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" hidden="1">
       <c r="A570">
         <v>569</v>
       </c>
@@ -12461,7 +12467,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" hidden="1">
       <c r="A571">
         <v>570</v>
       </c>
@@ -12475,7 +12481,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" hidden="1">
       <c r="A572">
         <v>571</v>
       </c>
@@ -12489,7 +12495,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" hidden="1">
       <c r="A573">
         <v>572</v>
       </c>
@@ -12503,7 +12509,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" hidden="1">
       <c r="A574">
         <v>573</v>
       </c>
@@ -12517,7 +12523,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" hidden="1">
       <c r="A575">
         <v>574</v>
       </c>
@@ -12531,7 +12537,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" hidden="1">
       <c r="A576">
         <v>575</v>
       </c>
@@ -12545,7 +12551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" hidden="1">
       <c r="A577">
         <v>576</v>
       </c>
@@ -12559,7 +12565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" hidden="1">
       <c r="A578">
         <v>577</v>
       </c>
@@ -12573,7 +12579,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" hidden="1">
       <c r="A579">
         <v>578</v>
       </c>
@@ -12587,7 +12593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" hidden="1">
       <c r="A580">
         <v>579</v>
       </c>
@@ -12601,7 +12607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" hidden="1">
       <c r="A581">
         <v>580</v>
       </c>
@@ -12615,7 +12621,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" hidden="1">
       <c r="A582">
         <v>581</v>
       </c>
@@ -12629,7 +12635,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" hidden="1">
       <c r="A583">
         <v>582</v>
       </c>
@@ -12643,7 +12649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" hidden="1">
       <c r="A584">
         <v>583</v>
       </c>
@@ -12657,7 +12663,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" hidden="1">
       <c r="A585">
         <v>584</v>
       </c>
@@ -12671,7 +12677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" hidden="1">
       <c r="A586">
         <v>585</v>
       </c>
@@ -12685,7 +12691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="587">
+    <row r="587" hidden="1">
       <c r="A587">
         <v>586</v>
       </c>
@@ -12699,7 +12705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="588">
+    <row r="588" hidden="1">
       <c r="A588">
         <v>587</v>
       </c>
@@ -12713,7 +12719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="589">
+    <row r="589" hidden="1">
       <c r="A589">
         <v>588</v>
       </c>
@@ -12727,7 +12733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="590">
+    <row r="590" hidden="1">
       <c r="A590">
         <v>589</v>
       </c>
@@ -12741,7 +12747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="591">
+    <row r="591" hidden="1">
       <c r="A591">
         <v>590</v>
       </c>
@@ -12755,7 +12761,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="592">
+    <row r="592" hidden="1">
       <c r="A592">
         <v>591</v>
       </c>
@@ -12769,7 +12775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="593">
+    <row r="593" hidden="1">
       <c r="A593">
         <v>592</v>
       </c>
@@ -12783,7 +12789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="594">
+    <row r="594" hidden="1">
       <c r="A594">
         <v>593</v>
       </c>
@@ -12797,7 +12803,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="595">
+    <row r="595" hidden="1">
       <c r="A595">
         <v>594</v>
       </c>
@@ -12811,7 +12817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="596">
+    <row r="596" hidden="1">
       <c r="A596">
         <v>595</v>
       </c>
@@ -12825,7 +12831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="597">
+    <row r="597" hidden="1">
       <c r="A597">
         <v>596</v>
       </c>
@@ -12839,7 +12845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="598">
+    <row r="598" hidden="1">
       <c r="A598">
         <v>597</v>
       </c>
@@ -12853,7 +12859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="599">
+    <row r="599" hidden="1">
       <c r="A599">
         <v>598</v>
       </c>
@@ -12867,7 +12873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="600">
+    <row r="600" hidden="1">
       <c r="A600">
         <v>599</v>
       </c>
@@ -12881,7 +12887,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="601">
+    <row r="601" hidden="1">
       <c r="A601">
         <v>600</v>
       </c>
@@ -12895,7 +12901,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="602">
+    <row r="602" hidden="1">
       <c r="A602">
         <v>601</v>
       </c>
@@ -12909,7 +12915,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="603">
+    <row r="603" hidden="1">
       <c r="A603">
         <v>602</v>
       </c>
@@ -12923,7 +12929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="604">
+    <row r="604" hidden="1">
       <c r="A604">
         <v>603</v>
       </c>
@@ -12937,7 +12943,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="605">
+    <row r="605" hidden="1">
       <c r="A605">
         <v>604</v>
       </c>
@@ -12951,7 +12957,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="606">
+    <row r="606" hidden="1">
       <c r="A606">
         <v>605</v>
       </c>
@@ -12965,7 +12971,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="607">
+    <row r="607" hidden="1">
       <c r="A607">
         <v>606</v>
       </c>
@@ -12979,7 +12985,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="608">
+    <row r="608" hidden="1">
       <c r="A608">
         <v>607</v>
       </c>
@@ -12993,7 +12999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="609">
+    <row r="609" hidden="1">
       <c r="A609">
         <v>608</v>
       </c>
@@ -13007,7 +13013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="610">
+    <row r="610" hidden="1">
       <c r="A610">
         <v>609</v>
       </c>
@@ -13021,7 +13027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="611">
+    <row r="611" hidden="1">
       <c r="A611">
         <v>610</v>
       </c>
@@ -13035,7 +13041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="612">
+    <row r="612" hidden="1">
       <c r="A612">
         <v>611</v>
       </c>
@@ -13049,7 +13055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="613">
+    <row r="613" hidden="1">
       <c r="A613">
         <v>612</v>
       </c>
@@ -13063,7 +13069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="614">
+    <row r="614" hidden="1">
       <c r="A614">
         <v>613</v>
       </c>
@@ -13077,7 +13083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="615">
+    <row r="615" hidden="1">
       <c r="A615">
         <v>614</v>
       </c>
@@ -13091,7 +13097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="616">
+    <row r="616" hidden="1">
       <c r="A616">
         <v>615</v>
       </c>
@@ -13105,7 +13111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="617">
+    <row r="617" hidden="1">
       <c r="A617">
         <v>616</v>
       </c>
@@ -13119,7 +13125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="618">
+    <row r="618" hidden="1">
       <c r="A618">
         <v>617</v>
       </c>
@@ -13133,7 +13139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="619">
+    <row r="619" hidden="1">
       <c r="A619">
         <v>618</v>
       </c>
@@ -13147,7 +13153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="620">
+    <row r="620" hidden="1">
       <c r="A620">
         <v>619</v>
       </c>
@@ -13161,7 +13167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="621">
+    <row r="621" hidden="1">
       <c r="A621">
         <v>620</v>
       </c>
@@ -13175,7 +13181,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="622">
+    <row r="622" hidden="1">
       <c r="A622">
         <v>621</v>
       </c>
@@ -13189,7 +13195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="623">
+    <row r="623" hidden="1">
       <c r="A623">
         <v>622</v>
       </c>
@@ -13203,7 +13209,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="624">
+    <row r="624" hidden="1">
       <c r="A624">
         <v>623</v>
       </c>
@@ -13217,7 +13223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="625">
+    <row r="625" hidden="1">
       <c r="A625">
         <v>624</v>
       </c>
@@ -13231,7 +13237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="626">
+    <row r="626" hidden="1">
       <c r="A626">
         <v>625</v>
       </c>
@@ -13245,7 +13251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="627">
+    <row r="627" hidden="1">
       <c r="A627">
         <v>626</v>
       </c>
@@ -13259,7 +13265,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="628">
+    <row r="628" hidden="1">
       <c r="A628">
         <v>627</v>
       </c>
@@ -13273,7 +13279,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="629">
+    <row r="629" hidden="1">
       <c r="A629">
         <v>628</v>
       </c>
@@ -13287,7 +13293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="630">
+    <row r="630" hidden="1">
       <c r="A630">
         <v>629</v>
       </c>
@@ -13301,7 +13307,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="631">
+    <row r="631" hidden="1">
       <c r="A631">
         <v>630</v>
       </c>
@@ -13315,7 +13321,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="632">
+    <row r="632" hidden="1">
       <c r="A632">
         <v>631</v>
       </c>
@@ -13329,7 +13335,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="633">
+    <row r="633" hidden="1">
       <c r="A633">
         <v>632</v>
       </c>
@@ -13343,7 +13349,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="634">
+    <row r="634" hidden="1">
       <c r="A634">
         <v>633</v>
       </c>
@@ -13357,7 +13363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="635">
+    <row r="635" hidden="1">
       <c r="A635">
         <v>634</v>
       </c>
@@ -13371,7 +13377,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="636">
+    <row r="636" hidden="1">
       <c r="A636">
         <v>635</v>
       </c>
@@ -13385,7 +13391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="637">
+    <row r="637" hidden="1">
       <c r="A637">
         <v>636</v>
       </c>
@@ -13399,7 +13405,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="638">
+    <row r="638" hidden="1">
       <c r="A638">
         <v>637</v>
       </c>
@@ -13413,7 +13419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="639">
+    <row r="639" hidden="1">
       <c r="A639">
         <v>638</v>
       </c>
@@ -13427,7 +13433,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="640">
+    <row r="640" hidden="1">
       <c r="A640">
         <v>639</v>
       </c>
@@ -13441,7 +13447,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="641">
+    <row r="641" hidden="1">
       <c r="A641">
         <v>640</v>
       </c>
@@ -13455,7 +13461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="642">
+    <row r="642" hidden="1">
       <c r="A642">
         <v>641</v>
       </c>
@@ -13469,7 +13475,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="643">
+    <row r="643" hidden="1">
       <c r="A643">
         <v>642</v>
       </c>
@@ -13483,7 +13489,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="644">
+    <row r="644" hidden="1">
       <c r="A644">
         <v>643</v>
       </c>
@@ -13497,7 +13503,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="645">
+    <row r="645" hidden="1">
       <c r="A645">
         <v>644</v>
       </c>
@@ -13511,7 +13517,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="646">
+    <row r="646" hidden="1">
       <c r="A646">
         <v>645</v>
       </c>
@@ -13525,7 +13531,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="647">
+    <row r="647" hidden="1">
       <c r="A647">
         <v>646</v>
       </c>
@@ -13539,7 +13545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="648">
+    <row r="648" hidden="1">
       <c r="A648">
         <v>647</v>
       </c>
@@ -13553,7 +13559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="649">
+    <row r="649" hidden="1">
       <c r="A649">
         <v>648</v>
       </c>
@@ -13567,7 +13573,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="650">
+    <row r="650" hidden="1">
       <c r="A650">
         <v>649</v>
       </c>
@@ -13581,7 +13587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="651">
+    <row r="651" hidden="1">
       <c r="A651">
         <v>650</v>
       </c>
@@ -13595,7 +13601,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="652">
+    <row r="652" hidden="1">
       <c r="A652">
         <v>651</v>
       </c>
@@ -13609,7 +13615,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="653">
+    <row r="653" hidden="1">
       <c r="A653">
         <v>652</v>
       </c>
@@ -13623,7 +13629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="654">
+    <row r="654" hidden="1">
       <c r="A654">
         <v>653</v>
       </c>
@@ -13637,7 +13643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="655">
+    <row r="655" hidden="1">
       <c r="A655">
         <v>654</v>
       </c>
@@ -13651,7 +13657,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="656">
+    <row r="656" hidden="1">
       <c r="A656">
         <v>655</v>
       </c>
@@ -13665,7 +13671,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657">
+    <row r="657" hidden="1">
       <c r="A657">
         <v>656</v>
       </c>
@@ -13679,7 +13685,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="658">
+    <row r="658" hidden="1">
       <c r="A658">
         <v>657</v>
       </c>
@@ -13693,7 +13699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="659">
+    <row r="659" hidden="1">
       <c r="A659">
         <v>658</v>
       </c>
@@ -13707,7 +13713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="660">
+    <row r="660" hidden="1">
       <c r="A660">
         <v>659</v>
       </c>
@@ -13721,7 +13727,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="661">
+    <row r="661" hidden="1">
       <c r="A661">
         <v>660</v>
       </c>
@@ -13735,7 +13741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="662">
+    <row r="662" hidden="1">
       <c r="A662">
         <v>661</v>
       </c>
@@ -13749,7 +13755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="663">
+    <row r="663" hidden="1">
       <c r="A663">
         <v>662</v>
       </c>
@@ -13763,7 +13769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="664">
+    <row r="664" hidden="1">
       <c r="A664">
         <v>663</v>
       </c>
@@ -13777,7 +13783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="665">
+    <row r="665" hidden="1">
       <c r="A665">
         <v>664</v>
       </c>
@@ -13791,7 +13797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="666">
+    <row r="666" hidden="1">
       <c r="A666">
         <v>665</v>
       </c>
@@ -13805,7 +13811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="667">
+    <row r="667" hidden="1">
       <c r="A667">
         <v>666</v>
       </c>
@@ -13819,7 +13825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="668">
+    <row r="668" hidden="1">
       <c r="A668">
         <v>667</v>
       </c>
@@ -13833,7 +13839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="669">
+    <row r="669" hidden="1">
       <c r="A669">
         <v>668</v>
       </c>
@@ -13847,7 +13853,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="670">
+    <row r="670" hidden="1">
       <c r="A670">
         <v>669</v>
       </c>
@@ -13861,7 +13867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="671">
+    <row r="671" hidden="1">
       <c r="A671">
         <v>670</v>
       </c>
@@ -13875,7 +13881,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="672">
+    <row r="672" hidden="1">
       <c r="A672">
         <v>671</v>
       </c>
@@ -13889,7 +13895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="673">
+    <row r="673" hidden="1">
       <c r="A673">
         <v>672</v>
       </c>
@@ -13903,7 +13909,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="674">
+    <row r="674" hidden="1">
       <c r="A674">
         <v>673</v>
       </c>
@@ -13917,7 +13923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="675">
+    <row r="675" hidden="1">
       <c r="A675">
         <v>674</v>
       </c>
@@ -13931,7 +13937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="676">
+    <row r="676" hidden="1">
       <c r="A676">
         <v>675</v>
       </c>
@@ -13945,7 +13951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="677">
+    <row r="677" hidden="1">
       <c r="A677">
         <v>676</v>
       </c>
@@ -13959,7 +13965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="678">
+    <row r="678" hidden="1">
       <c r="A678">
         <v>677</v>
       </c>
@@ -13973,7 +13979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679">
+    <row r="679" hidden="1">
       <c r="A679">
         <v>678</v>
       </c>
@@ -13987,7 +13993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="680">
+    <row r="680" hidden="1">
       <c r="A680">
         <v>679</v>
       </c>
@@ -14001,7 +14007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="681">
+    <row r="681" hidden="1">
       <c r="A681">
         <v>680</v>
       </c>
@@ -14015,7 +14021,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="682">
+    <row r="682" hidden="1">
       <c r="A682">
         <v>681</v>
       </c>
@@ -14029,7 +14035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="683">
+    <row r="683" hidden="1">
       <c r="A683">
         <v>682</v>
       </c>
@@ -14043,7 +14049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="684">
+    <row r="684" hidden="1">
       <c r="A684">
         <v>683</v>
       </c>
@@ -14057,7 +14063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="685">
+    <row r="685" hidden="1">
       <c r="A685">
         <v>684</v>
       </c>
@@ -14071,7 +14077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="686">
+    <row r="686" hidden="1">
       <c r="A686">
         <v>685</v>
       </c>
@@ -14085,7 +14091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="687">
+    <row r="687" hidden="1">
       <c r="A687">
         <v>686</v>
       </c>
@@ -14099,7 +14105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="688">
+    <row r="688" hidden="1">
       <c r="A688">
         <v>687</v>
       </c>
@@ -14113,7 +14119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="689">
+    <row r="689" hidden="1">
       <c r="A689">
         <v>688</v>
       </c>
@@ -14127,7 +14133,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="690">
+    <row r="690" hidden="1">
       <c r="A690">
         <v>689</v>
       </c>
@@ -14141,7 +14147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="691">
+    <row r="691" hidden="1">
       <c r="A691">
         <v>690</v>
       </c>
@@ -14155,7 +14161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="692">
+    <row r="692" hidden="1">
       <c r="A692">
         <v>691</v>
       </c>
@@ -14169,7 +14175,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="693">
+    <row r="693" hidden="1">
       <c r="A693">
         <v>692</v>
       </c>
@@ -14183,7 +14189,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="694">
+    <row r="694" hidden="1">
       <c r="A694">
         <v>693</v>
       </c>
@@ -14197,7 +14203,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="695">
+    <row r="695" hidden="1">
       <c r="A695">
         <v>694</v>
       </c>
@@ -14211,7 +14217,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="696">
+    <row r="696" hidden="1">
       <c r="A696">
         <v>695</v>
       </c>
@@ -14225,7 +14231,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="697">
+    <row r="697" hidden="1">
       <c r="A697">
         <v>696</v>
       </c>
@@ -14239,7 +14245,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="698">
+    <row r="698" hidden="1">
       <c r="A698">
         <v>697</v>
       </c>
@@ -14253,7 +14259,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="699">
+    <row r="699" hidden="1">
       <c r="A699">
         <v>698</v>
       </c>
@@ -14267,7 +14273,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="700">
+    <row r="700" hidden="1">
       <c r="A700">
         <v>699</v>
       </c>
@@ -14281,7 +14287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="701">
+    <row r="701" hidden="1">
       <c r="A701">
         <v>700</v>
       </c>
@@ -14295,7 +14301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="702">
+    <row r="702" hidden="1">
       <c r="A702">
         <v>701</v>
       </c>
@@ -14309,7 +14315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="703">
+    <row r="703" hidden="1">
       <c r="A703">
         <v>702</v>
       </c>
@@ -14323,7 +14329,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="704">
+    <row r="704" hidden="1">
       <c r="A704">
         <v>703</v>
       </c>
@@ -14337,7 +14343,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="705">
+    <row r="705" hidden="1">
       <c r="A705">
         <v>704</v>
       </c>
@@ -14351,7 +14357,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="706">
+    <row r="706" hidden="1">
       <c r="A706">
         <v>705</v>
       </c>
@@ -14365,7 +14371,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="707">
+    <row r="707" hidden="1">
       <c r="A707">
         <v>706</v>
       </c>
@@ -14379,7 +14385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="708">
+    <row r="708" hidden="1">
       <c r="A708">
         <v>707</v>
       </c>
@@ -14393,7 +14399,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="709">
+    <row r="709" hidden="1">
       <c r="A709">
         <v>708</v>
       </c>
@@ -14407,7 +14413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="710">
+    <row r="710" hidden="1">
       <c r="A710">
         <v>709</v>
       </c>
@@ -14421,7 +14427,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="711">
+    <row r="711" hidden="1">
       <c r="A711">
         <v>710</v>
       </c>
@@ -14435,7 +14441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="712">
+    <row r="712" hidden="1">
       <c r="A712">
         <v>711</v>
       </c>
@@ -14449,7 +14455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="713">
+    <row r="713" hidden="1">
       <c r="A713">
         <v>712</v>
       </c>
@@ -14463,7 +14469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="714">
+    <row r="714" hidden="1">
       <c r="A714">
         <v>713</v>
       </c>
@@ -14477,7 +14483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="715">
+    <row r="715" hidden="1">
       <c r="A715">
         <v>714</v>
       </c>
@@ -14491,7 +14497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="716">
+    <row r="716" hidden="1">
       <c r="A716">
         <v>715</v>
       </c>
@@ -14505,7 +14511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="717">
+    <row r="717" hidden="1">
       <c r="A717">
         <v>716</v>
       </c>
@@ -14519,7 +14525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="718">
+    <row r="718" hidden="1">
       <c r="A718">
         <v>717</v>
       </c>
@@ -14533,7 +14539,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="719">
+    <row r="719" hidden="1">
       <c r="A719">
         <v>718</v>
       </c>
@@ -14547,7 +14553,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="720">
+    <row r="720" hidden="1">
       <c r="A720">
         <v>719</v>
       </c>
@@ -14561,7 +14567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="721">
+    <row r="721" hidden="1">
       <c r="A721">
         <v>720</v>
       </c>
@@ -14575,7 +14581,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="722">
+    <row r="722" hidden="1">
       <c r="A722">
         <v>721</v>
       </c>
@@ -14589,7 +14595,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="723">
+    <row r="723" hidden="1">
       <c r="A723">
         <v>722</v>
       </c>
@@ -14603,7 +14609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="724">
+    <row r="724" hidden="1">
       <c r="A724">
         <v>723</v>
       </c>
@@ -14617,7 +14623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="725">
+    <row r="725" hidden="1">
       <c r="A725">
         <v>724</v>
       </c>
@@ -14631,7 +14637,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="726">
+    <row r="726" hidden="1">
       <c r="A726">
         <v>725</v>
       </c>
@@ -14645,7 +14651,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="727">
+    <row r="727" hidden="1">
       <c r="A727">
         <v>726</v>
       </c>
@@ -14659,7 +14665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="728">
+    <row r="728" hidden="1">
       <c r="A728">
         <v>727</v>
       </c>
@@ -14673,7 +14679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="729">
+    <row r="729" hidden="1">
       <c r="A729">
         <v>728</v>
       </c>
@@ -14687,7 +14693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="730">
+    <row r="730" hidden="1">
       <c r="A730">
         <v>729</v>
       </c>
@@ -14701,7 +14707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="731">
+    <row r="731" hidden="1">
       <c r="A731">
         <v>730</v>
       </c>
@@ -14715,7 +14721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="732">
+    <row r="732" hidden="1">
       <c r="A732">
         <v>731</v>
       </c>
@@ -14729,7 +14735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733">
+    <row r="733" hidden="1">
       <c r="A733">
         <v>732</v>
       </c>
@@ -14743,7 +14749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734">
+    <row r="734" hidden="1">
       <c r="A734">
         <v>733</v>
       </c>
@@ -14757,7 +14763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="735">
+    <row r="735" hidden="1">
       <c r="A735">
         <v>734</v>
       </c>
@@ -14771,7 +14777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="736">
+    <row r="736" hidden="1">
       <c r="A736">
         <v>735</v>
       </c>
@@ -14785,7 +14791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="737">
+    <row r="737" hidden="1">
       <c r="A737">
         <v>736</v>
       </c>
@@ -14799,7 +14805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="738">
+    <row r="738" hidden="1">
       <c r="A738">
         <v>737</v>
       </c>
@@ -14813,7 +14819,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="739">
+    <row r="739" hidden="1">
       <c r="A739">
         <v>738</v>
       </c>
@@ -14827,7 +14833,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="740">
+    <row r="740" hidden="1">
       <c r="A740">
         <v>739</v>
       </c>
@@ -14841,7 +14847,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="741">
+    <row r="741" hidden="1">
       <c r="A741">
         <v>740</v>
       </c>
@@ -14855,7 +14861,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="742">
+    <row r="742" hidden="1">
       <c r="A742">
         <v>741</v>
       </c>
@@ -14869,7 +14875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="743">
+    <row r="743" hidden="1">
       <c r="A743">
         <v>742</v>
       </c>
@@ -14883,7 +14889,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="744">
+    <row r="744" hidden="1">
       <c r="A744">
         <v>743</v>
       </c>
@@ -14897,7 +14903,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="745">
+    <row r="745" hidden="1">
       <c r="A745">
         <v>744</v>
       </c>
@@ -14911,7 +14917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="746">
+    <row r="746" hidden="1">
       <c r="A746">
         <v>745</v>
       </c>
@@ -14925,7 +14931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="747">
+    <row r="747" hidden="1">
       <c r="A747">
         <v>746</v>
       </c>
@@ -14939,7 +14945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="748">
+    <row r="748" hidden="1">
       <c r="A748">
         <v>747</v>
       </c>
@@ -14953,7 +14959,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="749">
+    <row r="749" hidden="1">
       <c r="A749">
         <v>748</v>
       </c>
@@ -14967,7 +14973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="750">
+    <row r="750" hidden="1">
       <c r="A750">
         <v>749</v>
       </c>
@@ -14981,7 +14987,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="751">
+    <row r="751" hidden="1">
       <c r="A751">
         <v>750</v>
       </c>
@@ -14995,7 +15001,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="752">
+    <row r="752" hidden="1">
       <c r="A752">
         <v>751</v>
       </c>
@@ -15009,7 +15015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="753">
+    <row r="753" hidden="1">
       <c r="A753">
         <v>752</v>
       </c>
@@ -15023,7 +15029,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="754">
+    <row r="754" hidden="1">
       <c r="A754">
         <v>753</v>
       </c>
@@ -15037,7 +15043,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="755">
+    <row r="755" hidden="1">
       <c r="A755">
         <v>754</v>
       </c>
@@ -15051,7 +15057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="756">
+    <row r="756" hidden="1">
       <c r="A756">
         <v>755</v>
       </c>
@@ -15065,7 +15071,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="757">
+    <row r="757" hidden="1">
       <c r="A757">
         <v>756</v>
       </c>
@@ -15079,7 +15085,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="758">
+    <row r="758" hidden="1">
       <c r="A758">
         <v>757</v>
       </c>
@@ -15093,7 +15099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="759">
+    <row r="759" hidden="1">
       <c r="A759">
         <v>758</v>
       </c>
@@ -15107,7 +15113,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="760">
+    <row r="760" hidden="1">
       <c r="A760">
         <v>759</v>
       </c>
@@ -15121,7 +15127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="761">
+    <row r="761" hidden="1">
       <c r="A761">
         <v>760</v>
       </c>
@@ -15135,7 +15141,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="762">
+    <row r="762" hidden="1">
       <c r="A762">
         <v>761</v>
       </c>
@@ -15149,7 +15155,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="763">
+    <row r="763" hidden="1">
       <c r="A763">
         <v>762</v>
       </c>
@@ -15163,7 +15169,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="764">
+    <row r="764" hidden="1">
       <c r="A764">
         <v>763</v>
       </c>
@@ -15177,7 +15183,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="765">
+    <row r="765" hidden="1">
       <c r="A765">
         <v>764</v>
       </c>
@@ -15191,7 +15197,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="766">
+    <row r="766" hidden="1">
       <c r="A766">
         <v>765</v>
       </c>
@@ -15205,7 +15211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="767">
+    <row r="767" hidden="1">
       <c r="A767">
         <v>766</v>
       </c>
@@ -15219,7 +15225,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="768">
+    <row r="768" hidden="1">
       <c r="A768">
         <v>767</v>
       </c>
@@ -15233,7 +15239,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="769">
+    <row r="769" hidden="1">
       <c r="A769">
         <v>768</v>
       </c>
@@ -15247,7 +15253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="770">
+    <row r="770" hidden="1">
       <c r="A770">
         <v>769</v>
       </c>
@@ -15261,7 +15267,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="771">
+    <row r="771" hidden="1">
       <c r="A771">
         <v>770</v>
       </c>
@@ -15275,7 +15281,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="772">
+    <row r="772" hidden="1">
       <c r="A772">
         <v>771</v>
       </c>
@@ -15289,7 +15295,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="773">
+    <row r="773" hidden="1">
       <c r="A773">
         <v>772</v>
       </c>
@@ -15303,7 +15309,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="774">
+    <row r="774" hidden="1">
       <c r="A774">
         <v>773</v>
       </c>
@@ -15317,7 +15323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="775">
+    <row r="775" hidden="1">
       <c r="A775">
         <v>774</v>
       </c>
@@ -15331,7 +15337,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="776">
+    <row r="776" hidden="1">
       <c r="A776">
         <v>775</v>
       </c>
@@ -15345,7 +15351,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="777">
+    <row r="777" hidden="1">
       <c r="A777">
         <v>776</v>
       </c>
@@ -15359,7 +15365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="778">
+    <row r="778" hidden="1">
       <c r="A778">
         <v>777</v>
       </c>
@@ -15373,7 +15379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="779">
+    <row r="779" hidden="1">
       <c r="A779">
         <v>778</v>
       </c>
@@ -15387,7 +15393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="780">
+    <row r="780" hidden="1">
       <c r="A780">
         <v>779</v>
       </c>
@@ -15401,7 +15407,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="781">
+    <row r="781" hidden="1">
       <c r="A781">
         <v>780</v>
       </c>
@@ -15415,7 +15421,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="782">
+    <row r="782" hidden="1">
       <c r="A782">
         <v>781</v>
       </c>
@@ -15429,7 +15435,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="783">
+    <row r="783" hidden="1">
       <c r="A783">
         <v>782</v>
       </c>
@@ -15443,7 +15449,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="784">
+    <row r="784" hidden="1">
       <c r="A784">
         <v>783</v>
       </c>
@@ -15457,7 +15463,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="785">
+    <row r="785" hidden="1">
       <c r="A785">
         <v>784</v>
       </c>
@@ -15471,7 +15477,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="786">
+    <row r="786" hidden="1">
       <c r="A786">
         <v>785</v>
       </c>
@@ -15485,7 +15491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="787">
+    <row r="787" hidden="1">
       <c r="A787">
         <v>786</v>
       </c>
@@ -15499,7 +15505,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="788">
+    <row r="788" hidden="1">
       <c r="A788">
         <v>787</v>
       </c>
@@ -15513,7 +15519,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="789">
+    <row r="789" hidden="1">
       <c r="A789">
         <v>788</v>
       </c>
@@ -15527,7 +15533,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="790">
+    <row r="790" hidden="1">
       <c r="A790">
         <v>789</v>
       </c>
@@ -15541,7 +15547,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="791">
+    <row r="791" hidden="1">
       <c r="A791">
         <v>790</v>
       </c>
@@ -15555,7 +15561,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="792">
+    <row r="792" hidden="1">
       <c r="A792">
         <v>791</v>
       </c>
@@ -15569,7 +15575,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="793">
+    <row r="793" hidden="1">
       <c r="A793">
         <v>792</v>
       </c>
@@ -15583,7 +15589,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="794">
+    <row r="794" hidden="1">
       <c r="A794">
         <v>793</v>
       </c>
@@ -15597,7 +15603,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="795">
+    <row r="795" hidden="1">
       <c r="A795">
         <v>794</v>
       </c>
@@ -15611,7 +15617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="796">
+    <row r="796" hidden="1">
       <c r="A796">
         <v>795</v>
       </c>
@@ -15625,7 +15631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="797">
+    <row r="797" hidden="1">
       <c r="A797">
         <v>796</v>
       </c>
@@ -15639,7 +15645,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="798">
+    <row r="798" hidden="1">
       <c r="A798">
         <v>797</v>
       </c>
@@ -15653,7 +15659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="799">
+    <row r="799" hidden="1">
       <c r="A799">
         <v>798</v>
       </c>
@@ -15667,7 +15673,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="800">
+    <row r="800" hidden="1">
       <c r="A800">
         <v>799</v>
       </c>
@@ -15681,7 +15687,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="801">
+    <row r="801" hidden="1">
       <c r="A801">
         <v>800</v>
       </c>
@@ -15695,7 +15701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="802">
+    <row r="802" hidden="1">
       <c r="A802">
         <v>801</v>
       </c>
@@ -15709,7 +15715,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="803">
+    <row r="803" hidden="1">
       <c r="A803">
         <v>802</v>
       </c>
@@ -15723,7 +15729,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="804">
+    <row r="804" hidden="1">
       <c r="A804">
         <v>803</v>
       </c>
@@ -15737,7 +15743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="805">
+    <row r="805" hidden="1">
       <c r="A805">
         <v>804</v>
       </c>
@@ -15751,7 +15757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="806">
+    <row r="806" hidden="1">
       <c r="A806">
         <v>805</v>
       </c>
@@ -15765,7 +15771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="807">
+    <row r="807" hidden="1">
       <c r="A807">
         <v>806</v>
       </c>
@@ -15779,7 +15785,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="808">
+    <row r="808" hidden="1">
       <c r="A808">
         <v>807</v>
       </c>
@@ -15793,7 +15799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="809">
+    <row r="809" hidden="1">
       <c r="A809">
         <v>808</v>
       </c>
@@ -15807,7 +15813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="810">
+    <row r="810" hidden="1">
       <c r="A810">
         <v>809</v>
       </c>
@@ -15821,7 +15827,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="811">
+    <row r="811" hidden="1">
       <c r="A811">
         <v>810</v>
       </c>
@@ -15835,7 +15841,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="812">
+    <row r="812" hidden="1">
       <c r="A812">
         <v>811</v>
       </c>
@@ -15849,7 +15855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="813">
+    <row r="813" hidden="1">
       <c r="A813">
         <v>812</v>
       </c>
@@ -15863,7 +15869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="814">
+    <row r="814" hidden="1">
       <c r="A814">
         <v>813</v>
       </c>
@@ -15877,7 +15883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="815">
+    <row r="815" hidden="1">
       <c r="A815">
         <v>814</v>
       </c>
@@ -15891,7 +15897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="816">
+    <row r="816" hidden="1">
       <c r="A816">
         <v>815</v>
       </c>
@@ -15905,7 +15911,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="817">
+    <row r="817" hidden="1">
       <c r="A817">
         <v>816</v>
       </c>
@@ -15919,7 +15925,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="818">
+    <row r="818" hidden="1">
       <c r="A818">
         <v>817</v>
       </c>
@@ -15933,7 +15939,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="819">
+    <row r="819" hidden="1">
       <c r="A819">
         <v>818</v>
       </c>
@@ -15947,7 +15953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="820">
+    <row r="820" hidden="1">
       <c r="A820">
         <v>819</v>
       </c>
@@ -15961,7 +15967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="821">
+    <row r="821" hidden="1">
       <c r="A821">
         <v>820</v>
       </c>
@@ -15975,7 +15981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="822">
+    <row r="822" hidden="1">
       <c r="A822">
         <v>821</v>
       </c>
@@ -15989,7 +15995,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="823">
+    <row r="823" hidden="1">
       <c r="A823">
         <v>822</v>
       </c>
@@ -16003,7 +16009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="824">
+    <row r="824" hidden="1">
       <c r="A824">
         <v>823</v>
       </c>
@@ -16017,7 +16023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="825">
+    <row r="825" hidden="1">
       <c r="A825">
         <v>824</v>
       </c>
@@ -16031,7 +16037,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="826">
+    <row r="826" hidden="1">
       <c r="A826">
         <v>825</v>
       </c>
@@ -16045,7 +16051,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="827">
+    <row r="827" hidden="1">
       <c r="A827">
         <v>826</v>
       </c>
@@ -16059,7 +16065,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="828">
+    <row r="828" hidden="1">
       <c r="A828">
         <v>827</v>
       </c>
@@ -16073,7 +16079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="829">
+    <row r="829" hidden="1">
       <c r="A829">
         <v>828</v>
       </c>
@@ -16087,7 +16093,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="830">
+    <row r="830" hidden="1">
       <c r="A830">
         <v>829</v>
       </c>
@@ -16101,7 +16107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="831">
+    <row r="831" hidden="1">
       <c r="A831">
         <v>830</v>
       </c>
@@ -16115,7 +16121,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="832">
+    <row r="832" hidden="1">
       <c r="A832">
         <v>831</v>
       </c>
@@ -16129,7 +16135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="833">
+    <row r="833" hidden="1">
       <c r="A833">
         <v>832</v>
       </c>
@@ -16143,7 +16149,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="834">
+    <row r="834" hidden="1">
       <c r="A834">
         <v>833</v>
       </c>
@@ -16157,7 +16163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="835">
+    <row r="835" hidden="1">
       <c r="A835">
         <v>834</v>
       </c>
@@ -16171,7 +16177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="836">
+    <row r="836" hidden="1">
       <c r="A836">
         <v>835</v>
       </c>
@@ -16185,7 +16191,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="837">
+    <row r="837" hidden="1">
       <c r="A837">
         <v>836</v>
       </c>
@@ -16199,7 +16205,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="838">
+    <row r="838" hidden="1">
       <c r="A838">
         <v>837</v>
       </c>
@@ -16213,7 +16219,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="839">
+    <row r="839" hidden="1">
       <c r="A839">
         <v>838</v>
       </c>
@@ -16227,7 +16233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="840">
+    <row r="840" hidden="1">
       <c r="A840">
         <v>839</v>
       </c>
@@ -16241,7 +16247,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="841">
+    <row r="841" hidden="1">
       <c r="A841">
         <v>840</v>
       </c>
@@ -16255,7 +16261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="842">
+    <row r="842" hidden="1">
       <c r="A842">
         <v>841</v>
       </c>
@@ -16269,7 +16275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="843">
+    <row r="843" hidden="1">
       <c r="A843">
         <v>842</v>
       </c>
@@ -16283,7 +16289,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="844">
+    <row r="844" hidden="1">
       <c r="A844">
         <v>843</v>
       </c>
@@ -16297,7 +16303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="845">
+    <row r="845" hidden="1">
       <c r="A845">
         <v>844</v>
       </c>
@@ -16311,7 +16317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="846">
+    <row r="846" hidden="1">
       <c r="A846">
         <v>845</v>
       </c>
@@ -16325,7 +16331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="847">
+    <row r="847" hidden="1">
       <c r="A847">
         <v>846</v>
       </c>
@@ -16339,7 +16345,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="848">
+    <row r="848" hidden="1">
       <c r="A848">
         <v>847</v>
       </c>
@@ -16353,7 +16359,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="849">
+    <row r="849" hidden="1">
       <c r="A849">
         <v>848</v>
       </c>
@@ -16367,7 +16373,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="850">
+    <row r="850" hidden="1">
       <c r="A850">
         <v>849</v>
       </c>
@@ -16381,7 +16387,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="851">
+    <row r="851" hidden="1">
       <c r="A851">
         <v>850</v>
       </c>
@@ -16395,7 +16401,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="852">
+    <row r="852" hidden="1">
       <c r="A852">
         <v>851</v>
       </c>
@@ -16409,7 +16415,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="853">
+    <row r="853" hidden="1">
       <c r="A853">
         <v>852</v>
       </c>
@@ -16423,7 +16429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="854">
+    <row r="854" hidden="1">
       <c r="A854">
         <v>853</v>
       </c>
@@ -16437,7 +16443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="855">
+    <row r="855" hidden="1">
       <c r="A855">
         <v>854</v>
       </c>
@@ -16451,7 +16457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="856">
+    <row r="856" hidden="1">
       <c r="A856">
         <v>855</v>
       </c>
@@ -16465,7 +16471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="857">
+    <row r="857" hidden="1">
       <c r="A857">
         <v>856</v>
       </c>
@@ -16479,7 +16485,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="858">
+    <row r="858" hidden="1">
       <c r="A858">
         <v>857</v>
       </c>
@@ -16493,7 +16499,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="859">
+    <row r="859" hidden="1">
       <c r="A859">
         <v>858</v>
       </c>
@@ -16507,7 +16513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="860">
+    <row r="860" hidden="1">
       <c r="A860">
         <v>859</v>
       </c>
@@ -16521,7 +16527,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="861">
+    <row r="861" hidden="1">
       <c r="A861">
         <v>860</v>
       </c>
@@ -16535,7 +16541,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="862">
+    <row r="862" hidden="1">
       <c r="A862">
         <v>861</v>
       </c>
@@ -16549,7 +16555,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="863">
+    <row r="863" hidden="1">
       <c r="A863">
         <v>862</v>
       </c>
@@ -16563,7 +16569,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="864">
+    <row r="864" hidden="1">
       <c r="A864">
         <v>863</v>
       </c>
@@ -16577,7 +16583,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="865">
+    <row r="865" hidden="1">
       <c r="A865">
         <v>864</v>
       </c>
@@ -16591,7 +16597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="866">
+    <row r="866" hidden="1">
       <c r="A866">
         <v>865</v>
       </c>
@@ -16605,7 +16611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="867">
+    <row r="867" hidden="1">
       <c r="A867">
         <v>866</v>
       </c>
@@ -16619,7 +16625,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="868">
+    <row r="868" hidden="1">
       <c r="A868">
         <v>867</v>
       </c>
@@ -16633,7 +16639,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="869">
+    <row r="869" hidden="1">
       <c r="A869">
         <v>868</v>
       </c>
@@ -16647,7 +16653,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="870">
+    <row r="870" hidden="1">
       <c r="A870">
         <v>869</v>
       </c>
@@ -16661,7 +16667,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="871">
+    <row r="871" hidden="1">
       <c r="A871">
         <v>870</v>
       </c>
@@ -16675,7 +16681,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="872">
+    <row r="872" hidden="1">
       <c r="A872">
         <v>871</v>
       </c>
@@ -16689,7 +16695,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="873">
+    <row r="873" hidden="1">
       <c r="A873">
         <v>872</v>
       </c>
@@ -16703,7 +16709,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="874">
+    <row r="874" hidden="1">
       <c r="A874">
         <v>873</v>
       </c>
@@ -16717,7 +16723,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="875">
+    <row r="875" hidden="1">
       <c r="A875">
         <v>874</v>
       </c>
@@ -16731,7 +16737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="876">
+    <row r="876" hidden="1">
       <c r="A876">
         <v>875</v>
       </c>
@@ -16745,7 +16751,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="877">
+    <row r="877" hidden="1">
       <c r="A877">
         <v>876</v>
       </c>
@@ -16759,7 +16765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="878">
+    <row r="878" hidden="1">
       <c r="A878">
         <v>877</v>
       </c>
@@ -16773,7 +16779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="879">
+    <row r="879" hidden="1">
       <c r="A879">
         <v>878</v>
       </c>
@@ -16787,7 +16793,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="880">
+    <row r="880" hidden="1">
       <c r="A880">
         <v>879</v>
       </c>
@@ -16801,7 +16807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="881">
+    <row r="881" hidden="1">
       <c r="A881">
         <v>880</v>
       </c>
@@ -16815,7 +16821,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="882">
+    <row r="882" hidden="1">
       <c r="A882">
         <v>881</v>
       </c>
@@ -16829,7 +16835,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="883">
+    <row r="883" hidden="1">
       <c r="A883">
         <v>882</v>
       </c>
@@ -16843,7 +16849,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="884">
+    <row r="884" hidden="1">
       <c r="A884">
         <v>883</v>
       </c>
@@ -16857,7 +16863,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="885">
+    <row r="885" hidden="1">
       <c r="A885">
         <v>884</v>
       </c>
@@ -16871,7 +16877,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="886">
+    <row r="886" hidden="1">
       <c r="A886">
         <v>885</v>
       </c>
@@ -16885,7 +16891,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="887">
+    <row r="887" hidden="1">
       <c r="A887">
         <v>886</v>
       </c>
@@ -16899,7 +16905,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="888">
+    <row r="888" hidden="1">
       <c r="A888">
         <v>887</v>
       </c>
@@ -16913,7 +16919,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="889">
+    <row r="889" hidden="1">
       <c r="A889">
         <v>888</v>
       </c>
@@ -16927,7 +16933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="890">
+    <row r="890" hidden="1">
       <c r="A890">
         <v>889</v>
       </c>
@@ -16941,7 +16947,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="891">
+    <row r="891" hidden="1">
       <c r="A891">
         <v>890</v>
       </c>
@@ -16955,7 +16961,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="892">
+    <row r="892" hidden="1">
       <c r="A892">
         <v>891</v>
       </c>
@@ -16969,7 +16975,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="893">
+    <row r="893" hidden="1">
       <c r="A893">
         <v>892</v>
       </c>
@@ -16983,7 +16989,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="894">
+    <row r="894" hidden="1">
       <c r="A894">
         <v>893</v>
       </c>
@@ -16997,7 +17003,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="895">
+    <row r="895" hidden="1">
       <c r="A895">
         <v>894</v>
       </c>
@@ -17011,7 +17017,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="896">
+    <row r="896" hidden="1">
       <c r="A896">
         <v>895</v>
       </c>
@@ -17025,7 +17031,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="897">
+    <row r="897" hidden="1">
       <c r="A897">
         <v>896</v>
       </c>
@@ -17039,7 +17045,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="898">
+    <row r="898" hidden="1">
       <c r="A898">
         <v>897</v>
       </c>
@@ -17053,7 +17059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="899">
+    <row r="899" hidden="1">
       <c r="A899">
         <v>898</v>
       </c>
@@ -17067,7 +17073,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="900">
+    <row r="900" hidden="1">
       <c r="A900">
         <v>899</v>
       </c>
@@ -17081,7 +17087,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="901">
+    <row r="901" hidden="1">
       <c r="A901">
         <v>900</v>
       </c>
@@ -17095,7 +17101,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="902">
+    <row r="902" hidden="1">
       <c r="A902">
         <v>901</v>
       </c>
@@ -17109,7 +17115,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="903">
+    <row r="903" hidden="1">
       <c r="A903">
         <v>902</v>
       </c>
@@ -17123,7 +17129,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="904">
+    <row r="904" hidden="1">
       <c r="A904">
         <v>903</v>
       </c>
@@ -17137,7 +17143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="905">
+    <row r="905" hidden="1">
       <c r="A905">
         <v>904</v>
       </c>
@@ -17151,7 +17157,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="906">
+    <row r="906" hidden="1">
       <c r="A906">
         <v>905</v>
       </c>
@@ -17165,7 +17171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="907">
+    <row r="907" hidden="1">
       <c r="A907">
         <v>906</v>
       </c>
@@ -17179,7 +17185,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="908">
+    <row r="908" hidden="1">
       <c r="A908">
         <v>907</v>
       </c>
@@ -17193,7 +17199,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="909">
+    <row r="909" hidden="1">
       <c r="A909">
         <v>908</v>
       </c>
@@ -17207,7 +17213,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="910">
+    <row r="910" hidden="1">
       <c r="A910">
         <v>909</v>
       </c>
@@ -17221,7 +17227,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="911">
+    <row r="911" hidden="1">
       <c r="A911">
         <v>910</v>
       </c>
@@ -17235,7 +17241,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="912">
+    <row r="912" hidden="1">
       <c r="A912">
         <v>911</v>
       </c>
@@ -17249,7 +17255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="913">
+    <row r="913" hidden="1">
       <c r="A913">
         <v>912</v>
       </c>
@@ -17263,7 +17269,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="914">
+    <row r="914" hidden="1">
       <c r="A914">
         <v>913</v>
       </c>
@@ -17277,7 +17283,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="915">
+    <row r="915" hidden="1">
       <c r="A915">
         <v>914</v>
       </c>
@@ -17291,7 +17297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="916">
+    <row r="916" hidden="1">
       <c r="A916">
         <v>915</v>
       </c>
@@ -17305,7 +17311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="917">
+    <row r="917" hidden="1">
       <c r="A917">
         <v>916</v>
       </c>
@@ -17319,7 +17325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="918">
+    <row r="918" hidden="1">
       <c r="A918">
         <v>917</v>
       </c>
@@ -17333,7 +17339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="919">
+    <row r="919" hidden="1">
       <c r="A919">
         <v>918</v>
       </c>
@@ -17347,7 +17353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="920">
+    <row r="920" hidden="1">
       <c r="A920">
         <v>919</v>
       </c>
@@ -17361,7 +17367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="921">
+    <row r="921" hidden="1">
       <c r="A921">
         <v>920</v>
       </c>
@@ -17375,7 +17381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="922">
+    <row r="922" hidden="1">
       <c r="A922">
         <v>921</v>
       </c>
@@ -17389,7 +17395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="923">
+    <row r="923" hidden="1">
       <c r="A923">
         <v>922</v>
       </c>
@@ -17403,7 +17409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="924">
+    <row r="924" hidden="1">
       <c r="A924">
         <v>923</v>
       </c>
@@ -17417,7 +17423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="925">
+    <row r="925" hidden="1">
       <c r="A925">
         <v>924</v>
       </c>
@@ -17431,7 +17437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="926">
+    <row r="926" hidden="1">
       <c r="A926">
         <v>925</v>
       </c>
@@ -17445,7 +17451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="927">
+    <row r="927" hidden="1">
       <c r="A927">
         <v>926</v>
       </c>
@@ -17459,7 +17465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="928">
+    <row r="928" hidden="1">
       <c r="A928">
         <v>927</v>
       </c>
@@ -17473,7 +17479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="929">
+    <row r="929" hidden="1">
       <c r="A929">
         <v>928</v>
       </c>
@@ -17487,7 +17493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="930">
+    <row r="930" hidden="1">
       <c r="A930">
         <v>929</v>
       </c>
@@ -17501,7 +17507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="931">
+    <row r="931" hidden="1">
       <c r="A931">
         <v>930</v>
       </c>
@@ -17515,7 +17521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="932">
+    <row r="932" hidden="1">
       <c r="A932">
         <v>931</v>
       </c>
@@ -17529,7 +17535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="933">
+    <row r="933" hidden="1">
       <c r="A933">
         <v>932</v>
       </c>
@@ -17543,7 +17549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="934">
+    <row r="934" hidden="1">
       <c r="A934">
         <v>933</v>
       </c>
@@ -17557,7 +17563,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="935">
+    <row r="935" hidden="1">
       <c r="A935">
         <v>934</v>
       </c>
@@ -17571,7 +17577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="936">
+    <row r="936" hidden="1">
       <c r="A936">
         <v>935</v>
       </c>
@@ -17585,7 +17591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="937">
+    <row r="937" hidden="1">
       <c r="A937">
         <v>936</v>
       </c>
@@ -17599,7 +17605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="938">
+    <row r="938" hidden="1">
       <c r="A938">
         <v>937</v>
       </c>
@@ -17613,7 +17619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="939">
+    <row r="939" hidden="1">
       <c r="A939">
         <v>938</v>
       </c>
@@ -17627,7 +17633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="940">
+    <row r="940" hidden="1">
       <c r="A940">
         <v>939</v>
       </c>
@@ -17641,7 +17647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="941">
+    <row r="941" hidden="1">
       <c r="A941">
         <v>940</v>
       </c>
@@ -17655,7 +17661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="942">
+    <row r="942" hidden="1">
       <c r="A942">
         <v>941</v>
       </c>
@@ -17669,7 +17675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="943">
+    <row r="943" hidden="1">
       <c r="A943">
         <v>942</v>
       </c>
@@ -17683,7 +17689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="944">
+    <row r="944" hidden="1">
       <c r="A944">
         <v>943</v>
       </c>
@@ -17697,7 +17703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="945">
+    <row r="945" hidden="1">
       <c r="A945">
         <v>944</v>
       </c>
@@ -17711,7 +17717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="946">
+    <row r="946" hidden="1">
       <c r="A946">
         <v>945</v>
       </c>
@@ -17725,7 +17731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="947">
+    <row r="947" hidden="1">
       <c r="A947">
         <v>946</v>
       </c>
@@ -17739,7 +17745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="948">
+    <row r="948" hidden="1">
       <c r="A948">
         <v>947</v>
       </c>
@@ -17753,7 +17759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="949">
+    <row r="949" hidden="1">
       <c r="A949">
         <v>948</v>
       </c>
@@ -17767,7 +17773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="950">
+    <row r="950" hidden="1">
       <c r="A950">
         <v>949</v>
       </c>
@@ -17781,7 +17787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="951">
+    <row r="951" hidden="1">
       <c r="A951">
         <v>950</v>
       </c>
@@ -17795,7 +17801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="952">
+    <row r="952" hidden="1">
       <c r="A952">
         <v>951</v>
       </c>
@@ -17809,7 +17815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="953">
+    <row r="953" hidden="1">
       <c r="A953">
         <v>952</v>
       </c>
@@ -17823,7 +17829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="954">
+    <row r="954" hidden="1">
       <c r="A954">
         <v>953</v>
       </c>
@@ -17837,7 +17843,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="955">
+    <row r="955" hidden="1">
       <c r="A955">
         <v>954</v>
       </c>
@@ -17851,7 +17857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="956">
+    <row r="956" hidden="1">
       <c r="A956">
         <v>955</v>
       </c>
@@ -17865,7 +17871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="957">
+    <row r="957" hidden="1">
       <c r="A957">
         <v>956</v>
       </c>
@@ -17879,7 +17885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="958">
+    <row r="958" hidden="1">
       <c r="A958">
         <v>957</v>
       </c>
@@ -17893,7 +17899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="959">
+    <row r="959" hidden="1">
       <c r="A959">
         <v>958</v>
       </c>
@@ -17907,7 +17913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="960">
+    <row r="960" hidden="1">
       <c r="A960">
         <v>959</v>
       </c>
@@ -17921,7 +17927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="961">
+    <row r="961" hidden="1">
       <c r="A961">
         <v>960</v>
       </c>
@@ -17935,7 +17941,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="962">
+    <row r="962" hidden="1">
       <c r="A962">
         <v>961</v>
       </c>
@@ -17949,7 +17955,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="963">
+    <row r="963" hidden="1">
       <c r="A963">
         <v>962</v>
       </c>
@@ -17963,7 +17969,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="964">
+    <row r="964" hidden="1">
       <c r="A964">
         <v>963</v>
       </c>
@@ -17977,7 +17983,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="965">
+    <row r="965" hidden="1">
       <c r="A965">
         <v>964</v>
       </c>
@@ -17991,7 +17997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="966">
+    <row r="966" hidden="1">
       <c r="A966">
         <v>965</v>
       </c>
@@ -18005,7 +18011,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="967">
+    <row r="967" hidden="1">
       <c r="A967">
         <v>966</v>
       </c>
@@ -18019,7 +18025,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="968">
+    <row r="968" hidden="1">
       <c r="A968">
         <v>967</v>
       </c>
@@ -18033,7 +18039,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="969">
+    <row r="969" hidden="1">
       <c r="A969">
         <v>968</v>
       </c>
@@ -18047,7 +18053,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="970">
+    <row r="970" hidden="1">
       <c r="A970">
         <v>969</v>
       </c>
@@ -18061,7 +18067,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="971">
+    <row r="971" hidden="1">
       <c r="A971">
         <v>970</v>
       </c>
@@ -18075,7 +18081,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="972">
+    <row r="972" hidden="1">
       <c r="A972">
         <v>971</v>
       </c>
@@ -18089,7 +18095,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="973">
+    <row r="973" hidden="1">
       <c r="A973">
         <v>972</v>
       </c>
@@ -18103,7 +18109,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="974">
+    <row r="974" hidden="1">
       <c r="A974">
         <v>973</v>
       </c>
@@ -18117,7 +18123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="975">
+    <row r="975" hidden="1">
       <c r="A975">
         <v>974</v>
       </c>
@@ -18131,7 +18137,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="976">
+    <row r="976" hidden="1">
       <c r="A976">
         <v>975</v>
       </c>
@@ -18145,7 +18151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="977">
+    <row r="977" hidden="1">
       <c r="A977">
         <v>976</v>
       </c>
@@ -18159,7 +18165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="978">
+    <row r="978" hidden="1">
       <c r="A978">
         <v>977</v>
       </c>
@@ -18173,7 +18179,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="979">
+    <row r="979" hidden="1">
       <c r="A979">
         <v>978</v>
       </c>
@@ -18187,7 +18193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="980">
+    <row r="980" hidden="1">
       <c r="A980">
         <v>979</v>
       </c>
@@ -18215,7 +18221,30 @@
         <v>10</v>
       </c>
     </row>
+    <row r="982" ht="14.25">
+      <c r="A982">
+        <v>981</v>
+      </c>
+      <c r="B982" t="s">
+        <v>37</v>
+      </c>
+      <c r="C982">
+        <v>9</v>
+      </c>
+      <c r="D982" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D982">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Allende"/>
+        <filter val="Ignacio Allende"/>
+        <filter val="Privada Ignacio Allende"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>

--- a/datos_municipio.xlsx
+++ b/datos_municipio.xlsx
@@ -18240,7 +18240,10 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="2" max="2" width="25.28125"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
